--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="639">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,1363 +44,1363 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dark matter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダークマター</t>
+  </si>
+  <si>
+    <t xml:space="preserve">void</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オーク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest,wooden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森から生まれし,木の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄塊と呼ばれる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グラナイト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rigid,stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">岩をも砕く,石の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">泥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">練習用の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森の草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深い草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">子供のおもちゃの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ゼリー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trembling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プルプルする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生もの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">食用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acacia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アカシア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">golden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄金に輝く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">銀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dreadbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闇を砕く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">銅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雷を帯し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bronze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青銅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">気高き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミカ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ephemeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">儚き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chromite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">クロム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unveiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真実を暴く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダイヤモンド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">everlasting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">変わることなき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rubynus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ルビナス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤く染まった</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">historic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">由緒ある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珊瑚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ocean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海からもたらされし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quartz sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珪砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glittering,glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">さざめく,ガラスの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水晶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">luminescent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異光を放つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">革</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mysterious</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全てを包む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">draconic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜を統べし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pearl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真珠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闇を照らす</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エメラルド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奇跡を呼ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cobalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コバルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adamantite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アダマンタイト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">earthshaking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大地を揺るがす</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sapphire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サファイア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">topaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">トパーズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquamarine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アクアマリン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オパール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翡翠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onyx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オニキス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lapis lazuli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラピス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ターコイズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meteorite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メテオライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platinum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brilliant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">光をまといし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">骨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immortal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不死なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">birch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">樺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">紙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふざけた</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エーテル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永遠なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パイン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森の土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ライムストーン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大理石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バサルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スレート</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diorite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダイオライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黒曜石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">godbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神殺しの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phyllite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フィライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hot spring water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">温泉水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pale soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">薄い色の土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mahogany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マホガニー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rosewood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローズウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">氷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">straw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">藁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farmwork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">農作業用の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cedar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mystic soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神秘的な土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mystic grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神秘的な草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">淡水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mithril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミスリル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ancient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">古なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">titanium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイタニアム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stainless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">色褪せぬ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cotton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">綿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightweight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">薄い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シルク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beautiful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">美しき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wrath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">逆鱗に触れし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cashmere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カシミア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">暖かなる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zylon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ザイロン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異国からもたらされし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spirit cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">霊布</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otherworldly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この世ならざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dawn cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宵晒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dusk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宵闇をまといし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">griffon scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翼鳥鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fallen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翼を折られし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プラスチック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transparent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">透き通った</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blue soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青い土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ウール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柔らかい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spider silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蜘蛛糸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entangled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">絡みつく</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">灰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">red soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">モミ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パルル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">light soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">明るい土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yellow soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色い土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sea water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tropical water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南の島の水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">white sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">麻</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">強靭なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">willow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cherryblossom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">桜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processed food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加工物</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">炭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poplar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポプラ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sea sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bamboo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amethyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アメジスト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bewitching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妖艶なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feywood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フェイウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coralwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コーラルウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rose quartz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローズクオーツ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lovely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">愛らしい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh cream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生クリーム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">琥珀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マグマ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">血</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">true obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真なる黒曜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lawbreaking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">摂理を断つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elder gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エルダーゴールド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄昏の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orichalcum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オリハルコン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unbreakable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">砕けることなき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深淵鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abyssal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深淵を映す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">netherite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ネザライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infernal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">煉獄で鍛えられし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternal sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infinite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無限の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unfading iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うつろわざる鉄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unfading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うつろわざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 19.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 11.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dark matter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダークマター</t>
-  </si>
-  <si>
-    <t xml:space="preserve">void</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オーク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest,wooden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森から生まれし,木の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄塊と呼ばれる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">granite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">グラナイト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rigid,stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">岩をも砕く,石の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">泥</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">practice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">練習用の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森の草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深い草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">子供のおもちゃの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ゼリー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trembling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プルプルする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生もの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">食用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acacia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アカシア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">golden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄金に輝く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">銀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dreadbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闇を砕く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">copper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">銅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lightning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雷を帯し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bronze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青銅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">気高き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミカ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ephemeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">儚き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chromite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">クロム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unveiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真実を暴く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diamond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダイヤモンド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">everlasting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">変わることなき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rubynus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ルビナス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤く染まった</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">historic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">由緒ある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">珊瑚</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ocean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海からもたらされし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quartz sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">珪砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glittering,glass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">さざめく,ガラスの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crystal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水晶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">luminescent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異光を放つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">革</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mysterious</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全てを包む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竜鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">draconic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竜を統べし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pearl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真珠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闇を照らす</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エメラルド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奇跡を呼ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cobalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コバルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adamantite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アダマンタイト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">earthshaking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大地を揺るがす</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapphire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">サファイア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">topaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">トパーズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aquamarine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アクアマリン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オパール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翡翠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onyx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オニキス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lapis lazuli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ラピス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ターコイズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meteorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メテオライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">platinum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brilliant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">光をまといし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">骨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">immortal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不死なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">birch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">樺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">paper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">紙</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ふざけた</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エーテル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eternal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永遠なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パイン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森の土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">limestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ライムストーン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大理石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">バサルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スレート</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダイオライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黒曜石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">godbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神殺しの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phyllite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フィライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hot spring water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">温泉水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pale soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">薄い色の土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mahogany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マホガニー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rosewood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ローズウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">氷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">straw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">藁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farmwork</t>
-  </si>
-  <si>
-    <t xml:space="preserve">農作業用の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cedar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">杉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mystic soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神秘的な土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mystic grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神秘的な草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresh water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">淡水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mithril</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミスリル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ancient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">古なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">titanium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タイタニアム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stainless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">色褪せぬ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cotton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">綿</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lightweight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">薄い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シルク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beautiful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">美しき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wrath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">逆鱗に触れし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cashmere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カシミア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">暖かなる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zylon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ザイロン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異国からもたらされし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spirit cloth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">霊布</t>
-  </si>
-  <si>
-    <t xml:space="preserve">otherworldly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">この世ならざる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dawn cloth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宵晒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dusk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宵闇をまといし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">griffon scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翼鳥鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fallen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翼を折られし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プラスチック</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transparent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">透き通った</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blue soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青い土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ウール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柔らかい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spider silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">蜘蛛糸</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entangled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">絡みつく</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">灰</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">red soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">モミ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">palulu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パルル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">light soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">明るい土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yellow soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄色い土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sea water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tropical water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">南の島の水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">white sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">麻</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">強靭なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">willow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cherryblossom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">桜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processed food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">加工物</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">炭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">poplar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ポプラ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sea sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bamboo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竹</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amethyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アメジスト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bewitching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妖艶なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feywood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フェイウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coralwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コーラルウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rose quartz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ローズクオーツ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lovely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">愛らしい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresh cream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生クリーム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">琥珀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">magma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マグマ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">血</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">true obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真なる黒曜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lawbreaking </t>
-  </si>
-  <si>
-    <t xml:space="preserve">摂理を断つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elder gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エルダーゴールド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄昏の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orichalcum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オリハルコン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unbreakable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">砕けることなき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深淵鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abyssal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深淵を映す</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">netherite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ネザライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infernal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">煉獄で鍛えられし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eternal sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infinite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無限の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unfading iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろわざる鉄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unfading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろわざる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 19.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 11.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.252</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 15.1</t>
@@ -2141,7 +2141,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C7" t="s">
         <v>474</v>
@@ -2189,7 +2189,7 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C9" t="s">
         <v>476</v>
@@ -2211,7 +2211,7 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C10" t="s">
         <v>477</v>
@@ -2311,7 +2311,7 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C14" t="s">
         <v>481</v>
@@ -2749,7 +2749,7 @@
         <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C31" t="s">
         <v>498</v>
@@ -2797,7 +2797,7 @@
         <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C33" t="s">
         <v>500</v>
@@ -2819,7 +2819,7 @@
         <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C34" t="s">
         <v>501</v>
@@ -2841,7 +2841,7 @@
         <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C35" t="s">
         <v>502</v>
@@ -2863,7 +2863,7 @@
         <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C36" t="s">
         <v>503</v>
@@ -2885,7 +2885,7 @@
         <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C37" t="s">
         <v>504</v>
@@ -2907,7 +2907,7 @@
         <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C38" t="s">
         <v>505</v>
@@ -2929,7 +2929,7 @@
         <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C39" t="s">
         <v>506</v>
@@ -2951,7 +2951,7 @@
         <v>170</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C40" t="s">
         <v>507</v>
@@ -2973,7 +2973,7 @@
         <v>173</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C41" t="s">
         <v>508</v>
@@ -3047,7 +3047,7 @@
         <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C44" t="s">
         <v>511</v>
@@ -3121,7 +3121,7 @@
         <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C47" t="s">
         <v>514</v>
@@ -3143,7 +3143,7 @@
         <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C48" t="s">
         <v>515</v>
@@ -3165,7 +3165,7 @@
         <v>205</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C49" t="s">
         <v>516</v>
@@ -3187,7 +3187,7 @@
         <v>208</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C50" t="s">
         <v>517</v>
@@ -3209,7 +3209,7 @@
         <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C51" t="s">
         <v>518</v>
@@ -3231,7 +3231,7 @@
         <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C52" t="s">
         <v>519</v>
@@ -3253,7 +3253,7 @@
         <v>217</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C53" t="s">
         <v>520</v>
@@ -3275,7 +3275,7 @@
         <v>220</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C54" t="s">
         <v>521</v>
@@ -3297,7 +3297,7 @@
         <v>223</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C55" t="s">
         <v>522</v>
@@ -3319,7 +3319,7 @@
         <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C56" t="s">
         <v>523</v>
@@ -3341,7 +3341,7 @@
         <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C57" t="s">
         <v>524</v>
@@ -3389,7 +3389,7 @@
         <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C59" t="s">
         <v>526</v>
@@ -3411,7 +3411,7 @@
         <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C60" t="s">
         <v>527</v>
@@ -3433,7 +3433,7 @@
         <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C61" t="s">
         <v>528</v>
@@ -3455,7 +3455,7 @@
         <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C62" t="s">
         <v>529</v>
@@ -3477,7 +3477,7 @@
         <v>249</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C63" t="s">
         <v>530</v>
@@ -3499,7 +3499,7 @@
         <v>252</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C64" t="s">
         <v>531</v>
@@ -3547,7 +3547,7 @@
         <v>260</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C66" t="s">
         <v>533</v>
@@ -3569,7 +3569,7 @@
         <v>263</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C67" t="s">
         <v>534</v>
@@ -3591,7 +3591,7 @@
         <v>266</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C68" t="s">
         <v>535</v>
@@ -3613,7 +3613,7 @@
         <v>269</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C69" t="s">
         <v>536</v>
@@ -3635,7 +3635,7 @@
         <v>272</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C70" t="s">
         <v>537</v>
@@ -3943,7 +3943,7 @@
         <v>330</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C82" t="s">
         <v>549</v>
@@ -4017,7 +4017,7 @@
         <v>343</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C85" t="s">
         <v>552</v>
@@ -4039,7 +4039,7 @@
         <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C86" t="s">
         <v>553</v>
@@ -4061,7 +4061,7 @@
         <v>349</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C87" t="s">
         <v>554</v>
@@ -4083,7 +4083,7 @@
         <v>352</v>
       </c>
       <c r="B88" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C88" t="s">
         <v>555</v>
@@ -4105,7 +4105,7 @@
         <v>355</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C89" t="s">
         <v>556</v>
@@ -4127,7 +4127,7 @@
         <v>358</v>
       </c>
       <c r="B90" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C90" t="s">
         <v>557</v>
@@ -4149,7 +4149,7 @@
         <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C91" t="s">
         <v>558</v>
@@ -4171,7 +4171,7 @@
         <v>364</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C92" t="s">
         <v>559</v>
@@ -4193,7 +4193,7 @@
         <v>367</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C93" t="s">
         <v>560</v>
@@ -4241,7 +4241,7 @@
         <v>375</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C95" t="s">
         <v>562</v>
@@ -4263,7 +4263,7 @@
         <v>378</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C96" t="s">
         <v>563</v>
@@ -4285,7 +4285,7 @@
         <v>381</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C97" t="s">
         <v>564</v>
@@ -4307,7 +4307,7 @@
         <v>384</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C98" t="s">
         <v>565</v>
@@ -4329,7 +4329,7 @@
         <v>387</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C99" t="s">
         <v>566</v>
@@ -4351,7 +4351,7 @@
         <v>390</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C100" t="s">
         <v>567</v>
@@ -4373,7 +4373,7 @@
         <v>393</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="C101" t="s">
         <v>568</v>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="647">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,1378 +44,1378 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dark matter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダークマター</t>
+  </si>
+  <si>
+    <t xml:space="preserve">void</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オーク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest,wooden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森から生まれし,木の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鉄塊と呼ばれる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グラナイト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rigid,stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">岩をも砕く,石の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">泥</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">練習用の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森の草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深い草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">子供のおもちゃの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jelly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ゼリー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trembling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プルプルする</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raw food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生もの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">食用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acacia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アカシア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">golden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄金に輝く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">銀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dreadbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闇を砕く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">copper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">銅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雷を帯し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bronze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青銅</t>
+  </si>
+  <si>
+    <t xml:space="preserve">noble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">気高き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミカ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ephemeral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">儚き</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chromite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">クロム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unveiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真実を暴く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダイヤモンド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">everlasting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">変わることなき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rubynus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ルビナス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crimson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤く染まった</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">historic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">由緒ある</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珊瑚</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ocean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海からもたらされし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quartz sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">珪砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glittering,glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">さざめく,ガラスの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crystal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水晶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">luminescent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異光を放つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">革</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mysterious</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全てを包む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dragon scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">draconic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竜を統べし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pearl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真珠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">闇を照らす</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emerald</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エメラルド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奇跡を呼ぶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cobalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コバルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adamantite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アダマンタイト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">earthshaking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大地を揺るがす</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sapphire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">サファイア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">topaz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">トパーズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquamarine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アクアマリン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">opal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オパール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翡翠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">onyx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オニキス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lapis lazuli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ラピス</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ターコイズ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meteorite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メテオライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platinum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brilliant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">光をまといし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">骨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immortal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不死なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">birch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">樺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">紙</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふざけた</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エーテル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永遠なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パイン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">forest soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">森の土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ライムストーン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大理石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">バサルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">スレート</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シルト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diorite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ダイオライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黒曜石</t>
+  </si>
+  <si>
+    <t xml:space="preserve">godbane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神殺しの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">phyllite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フィライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hot spring water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">温泉水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pale soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">薄い色の土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mahogany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マホガニー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rosewood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローズウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">氷</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">straw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">藁</t>
+  </si>
+  <si>
+    <t xml:space="preserve">farmwork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">農作業用の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cedar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mystic soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神秘的な土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mystic grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神秘的な草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">淡水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mithril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ミスリル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ancient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">古なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">titanium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">タイタニアム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stainless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">色褪せぬ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cotton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">綿</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightweight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">薄い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">シルク</t>
+  </si>
+  <si>
+    <t xml:space="preserve">beautiful</t>
+  </si>
+  <si>
+    <t xml:space="preserve">美しき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wrath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">逆鱗に触れし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cashmere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">カシミア</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">暖かなる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zylon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ザイロン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exotic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">異国からもたらされし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spirit cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">霊布</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otherworldly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">この世ならざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dawn cloth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宵晒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dusk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">宵闇をまといし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">griffon scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翼鳥鱗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fallen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">翼を折られし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">プラスチック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transparent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">透き通った</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blue soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">青い土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ウール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柔らかい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spider silk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">蜘蛛糸</t>
+  </si>
+  <si>
+    <t xml:space="preserve">entangled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">絡みつく</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">灰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">red soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">赤土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">モミ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">パルル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">light soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">明るい土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yellow soil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色い土</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sea water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tropical water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南の島の水</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">white sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hemp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">麻</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tough</t>
+  </si>
+  <si>
+    <t xml:space="preserve">強靭なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">willow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柳</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cherryblossom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">桜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">processed food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加工物</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">carbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">炭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">poplar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ポプラ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sea sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">海砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bamboo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">竹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amethyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アメジスト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bewitching</t>
+  </si>
+  <si>
+    <t xml:space="preserve">妖艶なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feywood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">フェイウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coralwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コーラルウッド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rose quartz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ローズクオーツ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lovely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">愛らしい</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fresh cream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">生クリーム</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">琥珀</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">マグマ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">血</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">true obsidian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真なる黒曜</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lawbreaking </t>
+  </si>
+  <si>
+    <t xml:space="preserve">摂理を断つ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">elder gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">エルダーゴールド</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄昏の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">orichalcum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">オリハルコン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unbreakable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">砕けることなき</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deep steel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深淵鋼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abyssal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">深淵を映す</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">netherite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ネザライト</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infernal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">煉獄で鍛えられし</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternal sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">永砂</t>
+  </si>
+  <si>
+    <t xml:space="preserve">infinite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無限の</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unfading iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うつろわざる鉄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unfading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">うつろわざる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雲</t>
+  </si>
+  <si>
+    <t xml:space="preserve">puffy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふわふわの</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EA 23.260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 19.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alpha 11.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">EA 23.295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dark matter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダークマター</t>
-  </si>
-  <si>
-    <t xml:space="preserve">void</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オーク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest,wooden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森から生まれし,木の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鉄塊と呼ばれる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">granite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">グラナイト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rigid,stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">岩をも砕く,石の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">泥</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">practice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">練習用の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森の草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深い草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">子供のおもちゃの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jelly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ゼリー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trembling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プルプルする</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">raw food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生もの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">edible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">食用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acacia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アカシア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">golden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄金に輝く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">銀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dreadbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闇を砕く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">copper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">銅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lightning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雷を帯し</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bronze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青銅</t>
-  </si>
-  <si>
-    <t xml:space="preserve">noble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">気高き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミカ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ephemeral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">儚き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chromite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">クロム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unveiling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真実を暴く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diamond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダイヤモンド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">everlasting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">変わることなき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rubynus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ルビナス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crimson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤く染まった</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">historic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">由緒ある</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">珊瑚</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ocean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海からもたらされし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">quartz sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">珪砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glittering,glass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">さざめく,ガラスの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crystal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水晶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">luminescent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異光を放つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">革</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mysterious</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全てを包む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dragon scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竜鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">draconic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竜を統べし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pearl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真珠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shining</t>
-  </si>
-  <si>
-    <t xml:space="preserve">闇を照らす</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emerald</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エメラルド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奇跡を呼ぶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cobalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コバルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">adamantite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アダマンタイト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">earthshaking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大地を揺るがす</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sapphire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">サファイア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">topaz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">トパーズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aquamarine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アクアマリン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">opal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オパール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翡翠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onyx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オニキス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lapis lazuli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ラピス</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">turquoise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ターコイズ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">meteorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メテオライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">platinum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brilliant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">光をまといし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">骨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">immortal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不死なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">birch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">樺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">paper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">紙</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ふざけた</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エーテル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eternal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永遠なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パイン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">forest soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">森の土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">limestone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ライムストーン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">marble</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大理石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basalt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">バサルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">スレート</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シルト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diorite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ダイオライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黒曜石</t>
-  </si>
-  <si>
-    <t xml:space="preserve">godbane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神殺しの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phyllite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フィライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hot spring water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">温泉水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pale soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">薄い色の土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mahogany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マホガニー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rosewood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ローズウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">氷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">straw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">藁</t>
-  </si>
-  <si>
-    <t xml:space="preserve">farmwork</t>
-  </si>
-  <si>
-    <t xml:space="preserve">農作業用の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cedar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">杉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mystic soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神秘的な土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mystic grass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神秘的な草</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresh water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">淡水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mithril</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ミスリル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ancient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">古なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69</t>
-  </si>
-  <si>
-    <t xml:space="preserve">titanium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タイタニアム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stainless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">色褪せぬ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cotton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">綿</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lightweight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">薄い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">シルク</t>
-  </si>
-  <si>
-    <t xml:space="preserve">beautiful</t>
-  </si>
-  <si>
-    <t xml:space="preserve">美しき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wrath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">逆鱗に触れし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cashmere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">カシミア</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">暖かなる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zylon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ザイロン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exotic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">異国からもたらされし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spirit cloth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">霊布</t>
-  </si>
-  <si>
-    <t xml:space="preserve">otherworldly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">この世ならざる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dawn cloth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宵晒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dusk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">宵闇をまといし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">griffon scale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翼鳥鱗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fallen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">翼を折られし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">プラスチック</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transparent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">透き通った</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blue soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">青い土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ウール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柔らかい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spider silk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">蜘蛛糸</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entangled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">絡みつく</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">灰</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">red soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">赤土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">モミ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">palulu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">パルル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">light soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">明るい土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yellow soil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄色い土</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sea water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tropical water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">南の島の水</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">white sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hemp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">麻</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">強靭なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">willow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">柳</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cherryblossom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">桜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">processed food</t>
-  </si>
-  <si>
-    <t xml:space="preserve">加工物</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">carbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">炭</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">poplar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ポプラ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sea sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">海砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bamboo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">竹</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amethyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アメジスト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bewitching</t>
-  </si>
-  <si>
-    <t xml:space="preserve">妖艶なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feywood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フェイウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coralwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コーラルウッド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rose quartz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ローズクオーツ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lovely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">愛らしい</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fresh cream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">生クリーム</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">amber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">琥珀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">magma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">マグマ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">血</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">true obsidian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真なる黒曜</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lawbreaking </t>
-  </si>
-  <si>
-    <t xml:space="preserve">摂理を断つ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elder gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">エルダーゴールド</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄昏の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orichalcum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">オリハルコン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unbreakable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">砕けることなき</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep steel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深淵鋼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abyssal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">深淵を映す</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">netherite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ネザライト</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infernal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">煉獄で鍛えられし</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eternal sand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">永砂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">infinite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">無限の</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unfading iron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろわざる鉄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unfading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">うつろわざる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雲</t>
-  </si>
-  <si>
-    <t xml:space="preserve">puffy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ふわふわの</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 19.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alpha 11.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 15.1</t>
@@ -2165,7 +2165,7 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C7" t="s">
         <v>480</v>
@@ -2213,7 +2213,7 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C9" t="s">
         <v>482</v>
@@ -2235,7 +2235,7 @@
         <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C10" t="s">
         <v>483</v>
@@ -2335,7 +2335,7 @@
         <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C14" t="s">
         <v>487</v>
@@ -2773,7 +2773,7 @@
         <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C31" t="s">
         <v>504</v>
@@ -2821,7 +2821,7 @@
         <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C33" t="s">
         <v>506</v>
@@ -2843,7 +2843,7 @@
         <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C34" t="s">
         <v>507</v>
@@ -2865,7 +2865,7 @@
         <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C35" t="s">
         <v>508</v>
@@ -2887,7 +2887,7 @@
         <v>158</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C36" t="s">
         <v>509</v>
@@ -2909,7 +2909,7 @@
         <v>161</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C37" t="s">
         <v>510</v>
@@ -2931,7 +2931,7 @@
         <v>164</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C38" t="s">
         <v>511</v>
@@ -2953,7 +2953,7 @@
         <v>167</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C39" t="s">
         <v>512</v>
@@ -2975,7 +2975,7 @@
         <v>170</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C40" t="s">
         <v>513</v>
@@ -2997,7 +2997,7 @@
         <v>173</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C41" t="s">
         <v>514</v>
@@ -3071,7 +3071,7 @@
         <v>186</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C44" t="s">
         <v>517</v>
@@ -3145,7 +3145,7 @@
         <v>199</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C47" t="s">
         <v>520</v>
@@ -3167,7 +3167,7 @@
         <v>202</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C48" t="s">
         <v>521</v>
@@ -3189,7 +3189,7 @@
         <v>205</v>
       </c>
       <c r="B49" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C49" t="s">
         <v>522</v>
@@ -3211,7 +3211,7 @@
         <v>208</v>
       </c>
       <c r="B50" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C50" t="s">
         <v>523</v>
@@ -3233,7 +3233,7 @@
         <v>211</v>
       </c>
       <c r="B51" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C51" t="s">
         <v>524</v>
@@ -3255,7 +3255,7 @@
         <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C52" t="s">
         <v>525</v>
@@ -3277,7 +3277,7 @@
         <v>217</v>
       </c>
       <c r="B53" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C53" t="s">
         <v>526</v>
@@ -3299,7 +3299,7 @@
         <v>220</v>
       </c>
       <c r="B54" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C54" t="s">
         <v>527</v>
@@ -3321,7 +3321,7 @@
         <v>223</v>
       </c>
       <c r="B55" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C55" t="s">
         <v>528</v>
@@ -3343,7 +3343,7 @@
         <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C56" t="s">
         <v>529</v>
@@ -3365,7 +3365,7 @@
         <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C57" t="s">
         <v>530</v>
@@ -3413,7 +3413,7 @@
         <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C59" t="s">
         <v>532</v>
@@ -3435,7 +3435,7 @@
         <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C60" t="s">
         <v>533</v>
@@ -3457,7 +3457,7 @@
         <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C61" t="s">
         <v>534</v>
@@ -3479,7 +3479,7 @@
         <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C62" t="s">
         <v>535</v>
@@ -3501,7 +3501,7 @@
         <v>249</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C63" t="s">
         <v>536</v>
@@ -3523,7 +3523,7 @@
         <v>252</v>
       </c>
       <c r="B64" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C64" t="s">
         <v>537</v>
@@ -3571,7 +3571,7 @@
         <v>260</v>
       </c>
       <c r="B66" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C66" t="s">
         <v>539</v>
@@ -3593,7 +3593,7 @@
         <v>263</v>
       </c>
       <c r="B67" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C67" t="s">
         <v>540</v>
@@ -3615,7 +3615,7 @@
         <v>266</v>
       </c>
       <c r="B68" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C68" t="s">
         <v>541</v>
@@ -3637,7 +3637,7 @@
         <v>269</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C69" t="s">
         <v>542</v>
@@ -3659,7 +3659,7 @@
         <v>272</v>
       </c>
       <c r="B70" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C70" t="s">
         <v>543</v>
@@ -3967,7 +3967,7 @@
         <v>330</v>
       </c>
       <c r="B82" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C82" t="s">
         <v>555</v>
@@ -4041,7 +4041,7 @@
         <v>343</v>
       </c>
       <c r="B85" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C85" t="s">
         <v>558</v>
@@ -4063,7 +4063,7 @@
         <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C86" t="s">
         <v>559</v>
@@ -4085,7 +4085,7 @@
         <v>349</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C87" t="s">
         <v>560</v>
@@ -4107,7 +4107,7 @@
         <v>352</v>
       </c>
       <c r="B88" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C88" t="s">
         <v>561</v>
@@ -4129,7 +4129,7 @@
         <v>355</v>
       </c>
       <c r="B89" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C89" t="s">
         <v>562</v>
@@ -4151,7 +4151,7 @@
         <v>358</v>
       </c>
       <c r="B90" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C90" t="s">
         <v>563</v>
@@ -4173,7 +4173,7 @@
         <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C91" t="s">
         <v>564</v>
@@ -4195,7 +4195,7 @@
         <v>364</v>
       </c>
       <c r="B92" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C92" t="s">
         <v>565</v>
@@ -4217,7 +4217,7 @@
         <v>367</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C93" t="s">
         <v>566</v>
@@ -4265,7 +4265,7 @@
         <v>375</v>
       </c>
       <c r="B95" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C95" t="s">
         <v>568</v>
@@ -4287,7 +4287,7 @@
         <v>378</v>
       </c>
       <c r="B96" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C96" t="s">
         <v>569</v>
@@ -4309,7 +4309,7 @@
         <v>381</v>
       </c>
       <c r="B97" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C97" t="s">
         <v>570</v>
@@ -4331,7 +4331,7 @@
         <v>384</v>
       </c>
       <c r="B98" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C98" t="s">
         <v>571</v>
@@ -4353,7 +4353,7 @@
         <v>387</v>
       </c>
       <c r="B99" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C99" t="s">
         <v>572</v>
@@ -4375,7 +4375,7 @@
         <v>390</v>
       </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C100" t="s">
         <v>573</v>
@@ -4397,7 +4397,7 @@
         <v>393</v>
       </c>
       <c r="B101" t="s">
-        <v>9</v>
+        <v>466</v>
       </c>
       <c r="C101" t="s">
         <v>574</v>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.307</t>
+    <t xml:space="preserve">EA 23.325</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Material.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Game/Material.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.325</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">dark matter</t>
